--- a/input/timetable/Магистратура_Менеджмент.xlsx
+++ b/input/timetable/Магистратура_Менеджмент.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="24" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="64">
   <si>
     <t>пара</t>
   </si>
@@ -72,6 +72,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -108,6 +111,9 @@
     <t>весенний</t>
   </si>
   <si>
+    <t>Попова Е.В.</t>
+  </si>
+  <si>
     <t>ЭУК</t>
   </si>
   <si>
@@ -141,9 +147,34 @@
     <t>Менеджмент в образовании            (ТО: 02.02.2026-23.03.2026)</t>
   </si>
   <si>
+    <t>Бутенко Н.А.</t>
+  </si>
+  <si>
+    <t>Бутенко Н.А./Попова Е.В.</t>
+  </si>
+  <si>
     <t>Основы научных исследований в области экономики и управления (лек), ЭОиДОТ// Современный стратегический анализ (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Open Sans"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Колосова О.Г</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Open Sans"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <t>Основы научных исследований в области экономики и управления (пр), ЭОиДОТ// Современный стратегический анализ (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -156,12 +187,18 @@
     <t>Технологии управления человеческими ресурсами (пр), ЭОиДОТ// Стратегическое планирование деятельности фирмы (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Курамшина А.В./Попова Е.В.</t>
+  </si>
+  <si>
     <t>Бизнес-моделирование и развитие компаний (пр), ЭОиДОТ</t>
   </si>
   <si>
     <t>Экономика персонала (пр). ЭОиДОТ// Современные стратегии и модели бизнес-управления (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Колосова О.Г./Попова Е.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> История и методология науки (пр),ЭОиДОТ// Современные стратегии и модели бизнес-управления (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -171,7 +208,16 @@
     <t>Практикум по межкультурной коммуникации (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Калантарян Г.А.</t>
+  </si>
+  <si>
+    <t>Богач М.А.</t>
+  </si>
+  <si>
     <t>Философия образования и современная образовательная политика (лек)/(пр), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Повзун В.Д.</t>
   </si>
   <si>
     <t>День самостоятельной работы</t>
@@ -278,7 +324,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,12 +343,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -382,6 +434,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -475,6 +585,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -620,6 +743,19 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -664,6 +800,21 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -751,7 +902,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -794,30 +945,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -842,107 +997,138 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -952,27 +1138,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1303,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1312,10 +1477,11 @@
     <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="18" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1323,15 +1489,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1339,39 +1505,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -1381,35 +1547,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
@@ -1420,257 +1586,308 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="26">
         <v>6</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="55"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="C10" s="80"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29">
         <v>7</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="83" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31">
+        <v>8</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="55" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="26">
+        <v>6</v>
+      </c>
+      <c r="C13" s="89"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="27"/>
+    </row>
+    <row r="14" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
+        <v>7</v>
+      </c>
+      <c r="C14" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="33"/>
+      <c r="B15" s="31">
+        <v>8</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="55" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="26">
+        <v>6</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="27"/>
+    </row>
+    <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29">
+        <v>7</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="33"/>
+      <c r="B18" s="31">
+        <v>8</v>
+      </c>
+      <c r="C18" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="56" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="26">
+        <v>6</v>
+      </c>
+      <c r="C19" s="67"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="27"/>
+    </row>
+    <row r="20" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
+        <v>7</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="33"/>
+      <c r="B21" s="31">
+        <v>8</v>
+      </c>
+      <c r="C21" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="26">
+        <v>6</v>
+      </c>
+      <c r="C22" s="61"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="27"/>
+    </row>
+    <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="34"/>
+      <c r="B23" s="29">
+        <v>7</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="35"/>
+      <c r="B24" s="31">
+        <v>8</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="26">
+        <v>1</v>
+      </c>
+      <c r="C25" s="67"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="42"/>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="40"/>
+      <c r="B26" s="26">
+        <v>2</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="37"/>
+      <c r="B27" s="29">
+        <v>3</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="41"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="38"/>
+      <c r="B28" s="39">
+        <v>4</v>
+      </c>
+      <c r="C28" s="73"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="49"/>
+    </row>
+    <row r="29" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="46"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="48"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="45"/>
+      <c r="B30" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="58"/>
-    </row>
-    <row r="12" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29">
-        <v>8</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="61"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="25">
-        <v>6</v>
-      </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="64"/>
-    </row>
-    <row r="14" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
-        <v>7</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="52"/>
-    </row>
-    <row r="15" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="31"/>
-      <c r="B15" s="29">
-        <v>8</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="52"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="25">
-        <v>6</v>
-      </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="70"/>
-    </row>
-    <row r="17" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
-        <v>7</v>
-      </c>
-      <c r="C17" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="52"/>
-    </row>
-    <row r="18" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="29">
-        <v>8</v>
-      </c>
-      <c r="C18" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="73"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="25">
-        <v>6</v>
-      </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="67"/>
-    </row>
-    <row r="20" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
-        <v>7</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="52"/>
-    </row>
-    <row r="21" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="31"/>
-      <c r="B21" s="29">
-        <v>8</v>
-      </c>
-      <c r="C21" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="52"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="25">
-        <v>6</v>
-      </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="70"/>
-    </row>
-    <row r="23" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="32"/>
-      <c r="B23" s="27">
-        <v>7</v>
-      </c>
-      <c r="C23" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="52"/>
-    </row>
-    <row r="24" spans="1:6" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="33"/>
-      <c r="B24" s="29">
-        <v>8</v>
-      </c>
-      <c r="C24" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="52"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="25">
-        <v>1</v>
-      </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="67"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="38"/>
-      <c r="B26" s="25">
-        <v>2</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="52"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="35"/>
-      <c r="B27" s="27">
-        <v>3</v>
-      </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="79"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="36"/>
-      <c r="B28" s="37">
-        <v>4</v>
-      </c>
-      <c r="C28" s="80"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="82"/>
-    </row>
-    <row r="29" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="49"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="40"/>
-      <c r="B30" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="75"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G31" s="43"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1683,13 +1900,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C21:F21"/>
@@ -1705,6 +1915,13 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -1735,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1744,10 +1961,11 @@
     <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1755,15 +1973,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1771,39 +1989,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -1813,35 +2031,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
@@ -1852,234 +2070,267 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="26">
         <v>6</v>
       </c>
-      <c r="C10" s="86" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="88"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="C10" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29">
         <v>7</v>
       </c>
-      <c r="C11" s="89"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="91"/>
-    </row>
-    <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29">
+      <c r="C11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="41"/>
+    </row>
+    <row r="12" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31">
         <v>8</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="61"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="25">
+      <c r="C12" s="86"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="56"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="26">
         <v>6</v>
       </c>
-      <c r="C13" s="86" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="88"/>
-    </row>
-    <row r="14" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="27"/>
+    </row>
+    <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
         <v>7</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="79"/>
-    </row>
-    <row r="15" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="31"/>
-      <c r="B15" s="29">
+      <c r="C14" s="70"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="41"/>
+    </row>
+    <row r="15" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="33"/>
+      <c r="B15" s="31">
         <v>8</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="79"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="25">
+      <c r="C15" s="70"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="41"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="26">
         <v>6</v>
       </c>
-      <c r="C16" s="86" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="88"/>
-    </row>
-    <row r="17" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="C16" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="27"/>
+    </row>
+    <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29">
         <v>7</v>
       </c>
-      <c r="C17" s="77"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="79"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="29">
+      <c r="C17" s="70"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="41"/>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="33"/>
+      <c r="B18" s="31">
         <v>8</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="73"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="25">
+      <c r="C18" s="92"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="56"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="26">
         <v>6</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="67"/>
-    </row>
-    <row r="20" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="C19" s="67"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="27"/>
+    </row>
+    <row r="20" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
         <v>7</v>
       </c>
-      <c r="C20" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="52"/>
-    </row>
-    <row r="21" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="31"/>
-      <c r="B21" s="29">
+      <c r="C20" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="55" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="33"/>
+      <c r="B21" s="31">
         <v>8</v>
       </c>
-      <c r="C21" s="71" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="73"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="25">
+      <c r="C21" s="92" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="93"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="56" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="26">
         <v>6</v>
       </c>
-      <c r="C22" s="86" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="87"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="88"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="32"/>
-      <c r="B23" s="27">
+      <c r="C22" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="27"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="34"/>
+      <c r="B23" s="29">
         <v>7</v>
       </c>
-      <c r="C23" s="77"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="79"/>
-    </row>
-    <row r="24" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="33"/>
-      <c r="B24" s="29">
+      <c r="C23" s="70"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="41"/>
+    </row>
+    <row r="24" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="35"/>
+      <c r="B24" s="31">
         <v>8</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="79"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="44">
+      <c r="C24" s="70"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="50"/>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="52">
         <v>1</v>
       </c>
-      <c r="C25" s="86"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="88"/>
-    </row>
-    <row r="26" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="38"/>
-      <c r="B26" s="25">
+      <c r="C25" s="95"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="27"/>
+    </row>
+    <row r="26" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="40"/>
+      <c r="B26" s="26">
         <v>2</v>
       </c>
-      <c r="C26" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="52"/>
-    </row>
-    <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="35"/>
-      <c r="B27" s="27">
+      <c r="C26" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="37"/>
+      <c r="B27" s="29">
         <v>3</v>
       </c>
-      <c r="C27" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="52"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="45"/>
-      <c r="B28" s="29">
+      <c r="C27" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="53"/>
+      <c r="B28" s="31">
         <v>4</v>
       </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="85"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C28" s="101"/>
+      <c r="D28" s="102"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="50"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G29" s="43"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>15</v>
       </c>
@@ -2089,6 +2340,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C10:F10"/>
@@ -2101,14 +2360,6 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5">
